--- a/data/trans_orig/P05A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>383505</t>
+          <t>384118</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>418109</t>
+          <t>415577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>367466</t>
+          <t>366403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>398439</t>
+          <t>399817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>760571</t>
+          <t>762375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>806354</t>
+          <t>807015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87882</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57946</t>
+          <t>55870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>86839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121405</t>
+          <t>121461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163911</t>
+          <t>162501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37795</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585804</t>
+          <t>581661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>625673</t>
+          <t>624364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472048</t>
+          <t>473628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515251</t>
+          <t>517523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1072758</t>
+          <t>1069474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1131388</t>
+          <t>1130310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>85711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>126237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>87264</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126157</t>
+          <t>125970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>184154</t>
+          <t>183965</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>236049</t>
+          <t>242357</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>499381</t>
+          <t>500663</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>538868</t>
+          <t>538992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>536966</t>
+          <t>535877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>579005</t>
+          <t>577132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1052284</t>
+          <t>1051455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1110243</t>
+          <t>1109301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74513</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110768</t>
+          <t>111867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83965</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121232</t>
+          <t>122584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166068</t>
+          <t>169333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218990</t>
+          <t>222149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>37457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62790</t>
+          <t>62394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>407571</t>
+          <t>404972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>444011</t>
+          <t>441120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>397536</t>
+          <t>395783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431921</t>
+          <t>431634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>814625</t>
+          <t>815707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>863874</t>
+          <t>866093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64774</t>
+          <t>66578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100041</t>
+          <t>101136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65861</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98408</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141611</t>
+          <t>140858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189012</t>
+          <t>190125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22631</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292950</t>
+          <t>293005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>323743</t>
+          <t>324227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313921</t>
+          <t>316607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>345059</t>
+          <t>346502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618028</t>
+          <t>619477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661721</t>
+          <t>661245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72988</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>97899</t>
+          <t>99989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138434</t>
+          <t>138535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37719</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232264</t>
+          <t>231118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255641</t>
+          <t>255856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276284</t>
+          <t>276777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>300343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>515178</t>
+          <t>516321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551532</t>
+          <t>551102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>31674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54095</t>
+          <t>52683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63997</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97106</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>164472</t>
+          <t>165068</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185201</t>
+          <t>185700</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>263623</t>
+          <t>263856</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292421</t>
+          <t>291918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>435722</t>
+          <t>437455</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>472624</t>
+          <t>471892</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42066</t>
+          <t>41967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61846</t>
+          <t>62599</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>61094</t>
+          <t>62182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95838</t>
+          <t>95195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2642423</t>
+          <t>2646875</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2726713</t>
+          <t>2730191</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2707237</t>
+          <t>2709781</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2801468</t>
+          <t>2799803</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5378735</t>
+          <t>5381129</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5504669</t>
+          <t>5509040</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>436667</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>515588</t>
+          <t>513509</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>466910</t>
+          <t>466603</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>553420</t>
+          <t>550222</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>926341</t>
+          <t>917937</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1042746</t>
+          <t>1033918</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>109152</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>165470</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>216873</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>374429</t>
+          <t>375963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404378</t>
+          <t>404161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366482</t>
+          <t>366017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>391756</t>
+          <t>392443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>751167</t>
+          <t>753975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>790490</t>
+          <t>789681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67105</t>
+          <t>64408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>71780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107066</t>
+          <t>107472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575794</t>
+          <t>575194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>612166</t>
+          <t>610480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506535</t>
+          <t>504860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>541097</t>
+          <t>540067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1093061</t>
+          <t>1094212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1143248</t>
+          <t>1142436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90204</t>
+          <t>90245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>119180</t>
+          <t>120226</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>166318</t>
+          <t>165301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>566525</t>
+          <t>563940</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>602602</t>
+          <t>603136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>584064</t>
+          <t>585583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>621897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1162141</t>
+          <t>1161448</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1215336</t>
+          <t>1215311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57688</t>
+          <t>58003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89416</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97142</t>
+          <t>96391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128255</t>
+          <t>127256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174957</t>
+          <t>177178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>54399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>506343</t>
+          <t>503827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>542682</t>
+          <t>541275</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513841</t>
+          <t>518025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>549947</t>
+          <t>552203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1032227</t>
+          <t>1033854</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1085389</t>
+          <t>1084325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50538</t>
+          <t>51084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>83431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49581</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82997</t>
+          <t>80185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107011</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>153577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45874</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>368737</t>
+          <t>365648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>393929</t>
+          <t>394001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>350690</t>
+          <t>352732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>383191</t>
+          <t>385365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>729793</t>
+          <t>730728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>769952</t>
+          <t>770956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71419</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76360</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112915</t>
+          <t>113472</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270966</t>
+          <t>270216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290748</t>
+          <t>290547</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>290138</t>
+          <t>289050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>313015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>567545</t>
+          <t>567281</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>597237</t>
+          <t>598544</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>33084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46917</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>76451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>210730</t>
+          <t>211008</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>231569</t>
+          <t>231697</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>338159</t>
+          <t>336874</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>361161</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>556812</t>
+          <t>554985</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>587175</t>
+          <t>588636</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>31283</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37754</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>62553</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>19172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2938863</t>
+          <t>2937924</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3021739</t>
+          <t>3019012</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3027798</t>
+          <t>3032703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3110370</t>
+          <t>3111893</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5988779</t>
+          <t>5994458</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6101308</t>
+          <t>6105418</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>304976</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>377476</t>
+          <t>376430</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>329938</t>
+          <t>325693</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>405077</t>
+          <t>400681</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>655334</t>
+          <t>659790</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>758307</t>
+          <t>763388</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>100482</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>94623</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>129674</t>
+          <t>128063</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345401</t>
+          <t>345192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374362</t>
+          <t>374313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300034</t>
+          <t>300279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330792</t>
+          <t>331183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654863</t>
+          <t>654784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>696185</t>
+          <t>697301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60174</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41927</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>68460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80997</t>
+          <t>79559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118764</t>
+          <t>120661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>43115</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462792</t>
+          <t>463856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502285</t>
+          <t>502150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441417</t>
+          <t>439386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475941</t>
+          <t>476424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917843</t>
+          <t>916046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>968405</t>
+          <t>970406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62271</t>
+          <t>62543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97728</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61813</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>95057</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>132208</t>
+          <t>131504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178402</t>
+          <t>179202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>37691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65358</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>548186</t>
+          <t>548157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>586525</t>
+          <t>587220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533735</t>
+          <t>534106</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>570884</t>
+          <t>570840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1094572</t>
+          <t>1097047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1146994</t>
+          <t>1150470</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65320</t>
+          <t>66007</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98770</t>
+          <t>100727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103055</t>
+          <t>102724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142309</t>
+          <t>140061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190247</t>
+          <t>188637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28869</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>517592</t>
+          <t>517011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>554554</t>
+          <t>555621</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526152</t>
+          <t>526555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563703</t>
+          <t>563595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1059603</t>
+          <t>1057612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1111932</t>
+          <t>1111241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63782</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97176</t>
+          <t>98017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85140</t>
+          <t>84911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>125467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170616</t>
+          <t>173688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>37684</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62619</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>377601</t>
+          <t>378054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>410577</t>
+          <t>411479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>394829</t>
+          <t>391268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>429617</t>
+          <t>426963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>781568</t>
+          <t>781335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>833405</t>
+          <t>832940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44415</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75080</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>76390</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96916</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141279</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58794</t>
+          <t>58521</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>268527</t>
+          <t>267711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>295411</t>
+          <t>295622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>299282</t>
+          <t>298953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>328168</t>
+          <t>329112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>575193</t>
+          <t>574895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>615705</t>
+          <t>616031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49682</t>
+          <t>48160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60558</t>
+          <t>61645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>64914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101568</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>209910</t>
+          <t>209303</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229676</t>
+          <t>229980</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>321808</t>
+          <t>322865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>354198</t>
+          <t>353392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>539727</t>
+          <t>540562</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>577436</t>
+          <t>577220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37934</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63723</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>60581</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94014</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2810143</t>
+          <t>2806456</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2894074</t>
+          <t>2893237</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2899210</t>
+          <t>2894161</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2989091</t>
+          <t>2986248</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5731159</t>
+          <t>5726231</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5856322</t>
+          <t>5849735</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368315</t>
+          <t>367523</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>441768</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>393223</t>
+          <t>394783</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>473483</t>
+          <t>480150</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>783832</t>
+          <t>785637</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>895715</t>
+          <t>900310</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>90057</t>
+          <t>90441</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>133003</t>
+          <t>131766</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>113129</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>213614</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>278476</t>
+          <t>280469</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>348497</t>
+          <t>349644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>382497</t>
+          <t>383617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256630</t>
+          <t>256971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288540</t>
+          <t>288451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>621322</t>
+          <t>620952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>665337</t>
+          <t>664590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47332</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65401</t>
+          <t>68122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37621</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360536</t>
+          <t>358639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393532</t>
+          <t>392769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459095</t>
+          <t>457938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490399</t>
+          <t>489857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>828203</t>
+          <t>829015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>873597</t>
+          <t>874101</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45363</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>88717</t>
+          <t>89023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28372</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>464966</t>
+          <t>465309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493364</t>
+          <t>495010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>526292</t>
+          <t>525893</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>552639</t>
+          <t>553174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>998246</t>
+          <t>999150</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1040680</t>
+          <t>1040238</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29526</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53880</t>
+          <t>53539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>25455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>60080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96337</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23589</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>799653</t>
+          <t>800623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>861293</t>
+          <t>861846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>628043</t>
+          <t>629005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>655032</t>
+          <t>654886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1438967</t>
+          <t>1437021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1515957</t>
+          <t>1519357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13835,12 +13835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64562</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41429</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>64660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57989</t>
+          <t>58531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120295</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>491196</t>
+          <t>490347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>516357</t>
+          <t>516841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14221,12 +14221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>473940</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495208</t>
+          <t>495638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>970975</t>
+          <t>973108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1004994</t>
+          <t>1005269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>53688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102269</t>
+          <t>100416</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>327025</t>
+          <t>326625</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>343327</t>
+          <t>343960</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>537121</t>
+          <t>537482</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>586765</t>
+          <t>591415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>872651</t>
+          <t>874006</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>932985</t>
+          <t>931966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14747,12 +14747,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79920</t>
+          <t>79481</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,12 +14860,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>251157</t>
+          <t>250494</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265606</t>
+          <t>265615</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>372479</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>389576</t>
+          <t>390374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>629671</t>
+          <t>630161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>651962</t>
+          <t>652230</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27847</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>23099</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61549</t>
+          <t>61137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3111175</t>
+          <t>3114691</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3221765</t>
+          <t>3219126</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3312526</t>
+          <t>3314224</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3415724</t>
+          <t>3415645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6452452</t>
+          <t>6452127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6599474</t>
+          <t>6597699</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>175934</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>259191</t>
+          <t>259850</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15702,12 +15702,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>214492</t>
+          <t>214691</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>297319</t>
+          <t>295560</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>416420</t>
+          <t>414946</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>531429</t>
+          <t>533341</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88858</t>
+          <t>88356</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15815,12 +15815,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>57999</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>94586</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>111445</t>
+          <t>114284</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>167690</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>384118</t>
+          <t>384178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>415577</t>
+          <t>416482</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366403</t>
+          <t>367021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>399817</t>
+          <t>399045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>762375</t>
+          <t>760005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>807015</t>
+          <t>805376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>55785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>85868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55870</t>
+          <t>57024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86839</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121461</t>
+          <t>122315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162501</t>
+          <t>165888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>26574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581661</t>
+          <t>585250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>624364</t>
+          <t>625006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473628</t>
+          <t>474001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517523</t>
+          <t>516632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1069474</t>
+          <t>1070758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1130310</t>
+          <t>1133126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85711</t>
+          <t>86381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126237</t>
+          <t>121974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87264</t>
+          <t>87360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125970</t>
+          <t>126075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>183965</t>
+          <t>182913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242357</t>
+          <t>238932</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29340</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28715</t>
+          <t>28871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56004</t>
+          <t>56535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500663</t>
+          <t>501444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>538992</t>
+          <t>539501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>535877</t>
+          <t>537254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>577132</t>
+          <t>580039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1051455</t>
+          <t>1050354</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1109301</t>
+          <t>1108567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76421</t>
+          <t>75025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111867</t>
+          <t>110402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>82639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122584</t>
+          <t>124168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169333</t>
+          <t>168108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222149</t>
+          <t>222015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>36354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>34534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62394</t>
+          <t>62232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>404972</t>
+          <t>404509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>441120</t>
+          <t>442494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>395783</t>
+          <t>396782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431634</t>
+          <t>432938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>815707</t>
+          <t>817062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>866093</t>
+          <t>866436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>66514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101136</t>
+          <t>102650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>64915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>99036</t>
+          <t>99509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140858</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190125</t>
+          <t>185951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>35365</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293005</t>
+          <t>294326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>324227</t>
+          <t>324653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316607</t>
+          <t>315385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346502</t>
+          <t>345695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619477</t>
+          <t>618235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>661245</t>
+          <t>660470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46792</t>
+          <t>46952</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>74991</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>73444</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99989</t>
+          <t>101180</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>138535</t>
+          <t>140157</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231118</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255856</t>
+          <t>255215</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276777</t>
+          <t>275974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>300343</t>
+          <t>300691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>516321</t>
+          <t>516350</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>551102</t>
+          <t>551458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>50088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31385</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52683</t>
+          <t>53373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62455</t>
+          <t>64614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94598</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,47 +3289,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>18656</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>11047</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>28285</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>18656</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>11041</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>27973</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>165068</t>
+          <t>164955</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185700</t>
+          <t>184575</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>263856</t>
+          <t>264665</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291918</t>
+          <t>292442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437455</t>
+          <t>436576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>471892</t>
+          <t>472416</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41967</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62599</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62182</t>
+          <t>62488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95195</t>
+          <t>96436</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2646875</t>
+          <t>2639528</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2730191</t>
+          <t>2724742</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2709781</t>
+          <t>2711913</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2799803</t>
+          <t>2804819</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5381129</t>
+          <t>5379320</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5509040</t>
+          <t>5502081</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>436005</t>
+          <t>437144</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>513509</t>
+          <t>518706</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>466603</t>
+          <t>463855</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>550222</t>
+          <t>549148</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>917937</t>
+          <t>930705</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1033918</t>
+          <t>1042153</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71632</t>
+          <t>72280</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110735</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>118849</t>
+          <t>119162</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>165470</t>
+          <t>161586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>216873</t>
+          <t>216013</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>375963</t>
+          <t>373299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>404161</t>
+          <t>403543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366017</t>
+          <t>367795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>392443</t>
+          <t>392482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>753975</t>
+          <t>751745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>789681</t>
+          <t>789649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64408</t>
+          <t>66213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>26704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>48950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>71701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107472</t>
+          <t>108501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575194</t>
+          <t>574349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>610480</t>
+          <t>611458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504860</t>
+          <t>507143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540067</t>
+          <t>541148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1094212</t>
+          <t>1092264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1142436</t>
+          <t>1141896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>55288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89736</t>
+          <t>89531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90245</t>
+          <t>87066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>120226</t>
+          <t>121539</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165301</t>
+          <t>167131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>563940</t>
+          <t>564317</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>603136</t>
+          <t>602337</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>585583</t>
+          <t>585191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>621897</t>
+          <t>623142</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1161448</t>
+          <t>1164205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1215311</t>
+          <t>1215656</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>56174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>92093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96391</t>
+          <t>95322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127256</t>
+          <t>128876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177178</t>
+          <t>174023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>31669</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,47 +5769,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>18730</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11210</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30744</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18730</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10815</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29519</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54399</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>503827</t>
+          <t>505255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541275</t>
+          <t>542694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518025</t>
+          <t>516485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>552203</t>
+          <t>551527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1033854</t>
+          <t>1033703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1084325</t>
+          <t>1082571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83431</t>
+          <t>82685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48227</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80185</t>
+          <t>82738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108504</t>
+          <t>109267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153577</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>365648</t>
+          <t>368141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394001</t>
+          <t>394260</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352732</t>
+          <t>351892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>385365</t>
+          <t>383773</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>730728</t>
+          <t>727682</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>770956</t>
+          <t>772401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53018</t>
+          <t>50705</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71924</t>
+          <t>70822</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74540</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113472</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>30953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270216</t>
+          <t>269959</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>290547</t>
+          <t>290615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>289050</t>
+          <t>291429</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>313015</t>
+          <t>314714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>567281</t>
+          <t>565670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>598544</t>
+          <t>598109</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>46569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76451</t>
+          <t>78442</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>211008</t>
+          <t>212403</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>231697</t>
+          <t>232463</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>336874</t>
+          <t>336731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>361161</t>
+          <t>361555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>554985</t>
+          <t>556952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>588636</t>
+          <t>588228</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62553</t>
+          <t>61390</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2937924</t>
+          <t>2941605</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3019012</t>
+          <t>3020455</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3032703</t>
+          <t>3027252</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3111893</t>
+          <t>3107761</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5994458</t>
+          <t>5991280</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6105418</t>
+          <t>6105060</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>302649</t>
+          <t>303839</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>376430</t>
+          <t>377097</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>325693</t>
+          <t>332649</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>400681</t>
+          <t>403887</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>659790</t>
+          <t>656914</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>763388</t>
+          <t>766019</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>94859</t>
+          <t>93258</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>130060</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>180409</t>
+          <t>182888</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345192</t>
+          <t>346889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374313</t>
+          <t>375200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300279</t>
+          <t>300259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>331183</t>
+          <t>331218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654784</t>
+          <t>654947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>697301</t>
+          <t>698343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60990</t>
+          <t>58790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41166</t>
+          <t>41299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68460</t>
+          <t>68365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79559</t>
+          <t>81789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120661</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463856</t>
+          <t>463186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502150</t>
+          <t>503570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>439386</t>
+          <t>441008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476424</t>
+          <t>476684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916046</t>
+          <t>914908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970406</t>
+          <t>969203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62543</t>
+          <t>60999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>96643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61699</t>
+          <t>61062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95057</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>131504</t>
+          <t>131933</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179202</t>
+          <t>178485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37691</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>37629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>548157</t>
+          <t>549363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>587220</t>
+          <t>587797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>534106</t>
+          <t>534386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>570840</t>
+          <t>571880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1097047</t>
+          <t>1098872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1150470</t>
+          <t>1149376</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>63801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100727</t>
+          <t>98318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>67783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102724</t>
+          <t>103037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140061</t>
+          <t>140011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>188513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28776</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>517011</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>555621</t>
+          <t>554927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526555</t>
+          <t>527068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563595</t>
+          <t>564535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1057612</t>
+          <t>1059971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1111241</t>
+          <t>1112330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63944</t>
+          <t>64143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98017</t>
+          <t>96148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>53173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84911</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125467</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173688</t>
+          <t>170555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>39275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60926</t>
+          <t>63124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>378054</t>
+          <t>378284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>411479</t>
+          <t>412463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>391268</t>
+          <t>393332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>426963</t>
+          <t>428811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>781335</t>
+          <t>782551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>832940</t>
+          <t>831648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44415</t>
+          <t>43902</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73379</t>
+          <t>75154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>43679</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76390</t>
+          <t>75726</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139463</t>
+          <t>138318</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58521</t>
+          <t>63655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10779,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>267711</t>
+          <t>267132</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>295622</t>
+          <t>294297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>298953</t>
+          <t>298823</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>329112</t>
+          <t>329072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>574895</t>
+          <t>578445</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>616031</t>
+          <t>618156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48160</t>
+          <t>49005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61645</t>
+          <t>61230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>64112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>98009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -11235,12 +11235,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>209303</t>
+          <t>210762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229980</t>
+          <t>229969</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>322865</t>
+          <t>322368</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>353392</t>
+          <t>354781</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>540562</t>
+          <t>539253</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>577220</t>
+          <t>576980</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39101</t>
+          <t>36760</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34195</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>64791</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60581</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93890</t>
+          <t>96542</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2806456</t>
+          <t>2812514</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2893237</t>
+          <t>2894719</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2894161</t>
+          <t>2897928</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2986248</t>
+          <t>2989431</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5726231</t>
+          <t>5729540</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5849735</t>
+          <t>5856991</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>367523</t>
+          <t>367860</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>441768</t>
+          <t>443425</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>394783</t>
+          <t>393553</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>480150</t>
+          <t>474246</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>785637</t>
+          <t>788685</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>900310</t>
+          <t>901700</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>90441</t>
+          <t>89691</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131766</t>
+          <t>131415</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>115479</t>
+          <t>115967</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>164123</t>
+          <t>161495</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>215007</t>
+          <t>211260</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280469</t>
+          <t>278521</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>370330</t>
+          <t>379634</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>349644</t>
+          <t>360835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>383617</t>
+          <t>392417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>274808</t>
+          <t>316652</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>296185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288451</t>
+          <t>329915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>645137</t>
+          <t>696286</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620952</t>
+          <t>669270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>664590</t>
+          <t>716195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>31662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29652</t>
+          <t>33656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>51304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>45429</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68122</t>
+          <t>71892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>312874</t>
+          <t>358447</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312874</t>
+          <t>358447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312874</t>
+          <t>358447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>708989</t>
+          <t>762825</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>708989</t>
+          <t>762825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>708989</t>
+          <t>762825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>378755</t>
+          <t>425392</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358639</t>
+          <t>404729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392769</t>
+          <t>441185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>473209</t>
+          <t>458961</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457938</t>
+          <t>444465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>489857</t>
+          <t>469742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>851964</t>
+          <t>884352</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829015</t>
+          <t>860000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874101</t>
+          <t>902080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51639</t>
+          <t>61483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,32 +12981,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>48448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>67717</t>
+          <t>76660</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89023</t>
+          <t>97748</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,22 +13129,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>29064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935481</t>
+          <t>977647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>481218</t>
+          <t>556063</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>465309</t>
+          <t>537483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>495010</t>
+          <t>570190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>560593</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>525893</t>
+          <t>546938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>553174</t>
+          <t>571732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1019959</t>
+          <t>1116657</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>999150</t>
+          <t>1094772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1040238</t>
+          <t>1134825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36542</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47971</t>
+          <t>56002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76709</t>
+          <t>91108</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60080</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -13515,22 +13515,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>41854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>533870</t>
+          <t>616321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>533870</t>
+          <t>616321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>533870</t>
+          <t>616321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>589117</t>
+          <t>620194</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>589117</t>
+          <t>620194</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>589117</t>
+          <t>620194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1122987</t>
+          <t>1236516</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1122987</t>
+          <t>1236516</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1122987</t>
+          <t>1236516</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>828012</t>
+          <t>631767</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>800623</t>
+          <t>615492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>861846</t>
+          <t>647760</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>641167</t>
+          <t>656713</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>629005</t>
+          <t>642992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654886</t>
+          <t>669698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1469179</t>
+          <t>1288480</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1437021</t>
+          <t>1266335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1519357</t>
+          <t>1308473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42168</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65460</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>59160</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41411</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64660</t>
+          <t>71715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>94978</t>
+          <t>106758</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>90930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>127067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>884232</t>
+          <t>697152</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884232</t>
+          <t>697152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>884232</t>
+          <t>697152</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>708633</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>708633</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>708633</t>
+          <t>732085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1592865</t>
+          <t>1429237</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1592865</t>
+          <t>1429237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1592865</t>
+          <t>1429237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>504164</t>
+          <t>548550</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>490347</t>
+          <t>533796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>516841</t>
+          <t>560719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>485848</t>
+          <t>539717</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>473940</t>
+          <t>527149</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495638</t>
+          <t>549870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>990013</t>
+          <t>1088267</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>973108</t>
+          <t>1070180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1005269</t>
+          <t>1106425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -14314,17 +14314,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41753</t>
+          <t>45360</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54867</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>48887</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,17 +14384,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>94247</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>79449</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100416</t>
+          <t>110952</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>26591</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>555648</t>
+          <t>603746</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>555648</t>
+          <t>603746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>555648</t>
+          <t>603746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>544710</t>
+          <t>605359</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>544710</t>
+          <t>605359</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>544710</t>
+          <t>605359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1100359</t>
+          <t>1209105</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1100359</t>
+          <t>1209105</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1100359</t>
+          <t>1209105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>335594</t>
+          <t>370310</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>326625</t>
+          <t>360052</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>343960</t>
+          <t>378810</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>561872</t>
+          <t>388666</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>537482</t>
+          <t>378889</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>591415</t>
+          <t>397289</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>897466</t>
+          <t>758975</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>874006</t>
+          <t>745138</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>931966</t>
+          <t>772666</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33936</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33370</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>65068</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>52973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79481</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367582</t>
+          <t>406492</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367582</t>
+          <t>406492</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367582</t>
+          <t>406492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>603852</t>
+          <t>433780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>603852</t>
+          <t>433780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>603852</t>
+          <t>433780</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>971434</t>
+          <t>840271</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>971434</t>
+          <t>840271</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>971434</t>
+          <t>840271</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>259069</t>
+          <t>283462</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>250494</t>
+          <t>273682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265615</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>382320</t>
+          <t>416504</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>373315</t>
+          <t>405020</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>390374</t>
+          <t>425099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>641389</t>
+          <t>699965</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>630161</t>
+          <t>686000</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>652230</t>
+          <t>712331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>42342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,32 +15296,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>50525</t>
+          <t>56039</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>45376</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61137</t>
+          <t>69042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282155</t>
+          <t>309504</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>419339</t>
+          <t>457484</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>419339</t>
+          <t>457484</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>419339</t>
+          <t>457484</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>701494</t>
+          <t>766987</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>701494</t>
+          <t>766987</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>701494</t>
+          <t>766987</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3157141</t>
+          <t>3195178</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3114691</t>
+          <t>3151438</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3219126</t>
+          <t>3229038</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3357966</t>
+          <t>3337805</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3314224</t>
+          <t>3303422</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3415645</t>
+          <t>3371636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>6515106</t>
+          <t>6532984</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6452127</t>
+          <t>6477671</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6597699</t>
+          <t>6580741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>221278</t>
+          <t>250664</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>175934</t>
+          <t>221249</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>259850</t>
+          <t>288881</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>258962</t>
+          <t>289059</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>214691</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>295560</t>
+          <t>320087</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>480240</t>
+          <t>539722</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>414946</t>
+          <t>497686</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>533341</t>
+          <t>590035</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>64730</t>
+          <t>68641</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>52444</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88356</t>
+          <t>93302</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>73532</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>94586</t>
+          <t>99838</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>138262</t>
+          <t>149883</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>114284</t>
+          <t>128358</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>170204</t>
+          <t>177613</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3443150</t>
+          <t>3514483</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3690459</t>
+          <t>3708105</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7133608</t>
+          <t>7222589</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
